--- a/Figuras/Descriptiva/Tabla_resumen_periodo.xlsx
+++ b/Figuras/Descriptiva/Tabla_resumen_periodo.xlsx
@@ -32,10 +32,10 @@
     <t xml:space="preserve">Mínimo</t>
   </si>
   <si>
-    <t xml:space="preserve">Previo a restricciones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Durante las restricciones</t>
+    <t xml:space="preserve">Sin restricciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con restricciones</t>
   </si>
 </sst>
 </file>
@@ -389,13 +389,13 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>14469.356</v>
+        <v>14273.97</v>
       </c>
       <c r="C2" t="n">
-        <v>14756</v>
+        <v>14346</v>
       </c>
       <c r="D2" t="n">
-        <v>8365.638</v>
+        <v>8346.437</v>
       </c>
       <c r="E2" t="n">
         <v>29335</v>
@@ -409,16 +409,16 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>8673.004</v>
+        <v>7663.316</v>
       </c>
       <c r="C3" t="n">
-        <v>6447</v>
+        <v>5573</v>
       </c>
       <c r="D3" t="n">
-        <v>6879.41</v>
+        <v>6158.284</v>
       </c>
       <c r="E3" t="n">
-        <v>28013</v>
+        <v>24216</v>
       </c>
       <c r="F3" t="n">
         <v>184</v>
